--- a/prices.xlsx
+++ b/prices.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="89">
   <si>
     <t>Component</t>
   </si>
@@ -262,6 +262,27 @@
   </si>
   <si>
     <t>128GB DDR5 ECC RDIMM</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>CPU or Processor</t>
+  </si>
+  <si>
+    <t>GPU</t>
+  </si>
+  <si>
+    <t>Nvidia GPU</t>
+  </si>
+  <si>
+    <t>AMD GPU</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>RAM</t>
   </si>
 </sst>
 </file>
@@ -600,657 +621,901 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>14042</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>28910</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>37760</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>43070</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>46610</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>57820</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>53100</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>70210</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>36580</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>36580</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>37760</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>38940</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="C15">
         <v>44840</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>60180</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>61360</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>61360</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>62540</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>63720</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
         <v>20</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>73750</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
         <v>21</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>72570</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
         <v>22</v>
       </c>
-      <c r="B23">
+      <c r="C23">
         <v>70800</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" t="s">
         <v>23</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>108560</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
         <v>24</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>108560</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="B26">
+      <c r="C26">
         <v>110920</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" t="s">
         <v>26</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>110920</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
         <v>27</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>141600</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s">
         <v>28</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>149860</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" t="s">
         <v>29</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>149860</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" t="s">
         <v>30</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>149860</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" t="s">
         <v>31</v>
       </c>
-      <c r="B32">
+      <c r="C32">
         <v>149860</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" t="s">
         <v>32</v>
       </c>
-      <c r="B33">
+      <c r="C33">
         <v>162840</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" t="s">
         <v>33</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>354000</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" t="s">
         <v>34</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>389400</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" t="s">
         <v>35</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>389400</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" t="s">
         <v>36</v>
       </c>
-      <c r="B37">
+      <c r="C37">
         <v>395300</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" t="s">
         <v>37</v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>395300</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" t="s">
         <v>38</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>407100</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" t="s">
         <v>39</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>424800</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" t="s">
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>436600</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s">
         <v>41</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>495600</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
         <v>42</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>24780</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>31270</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" t="s">
         <v>44</v>
       </c>
-      <c r="B46">
+      <c r="C46">
         <v>47200</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
         <v>45</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>48380</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" t="s">
         <v>46</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <v>59590</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" t="s">
         <v>47</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <v>73750</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" t="s">
         <v>48</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <v>75520</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" t="s">
         <v>49</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>159300</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" t="s">
         <v>50</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>920400</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>87</v>
+      </c>
+      <c r="B55" t="s">
         <v>51</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <v>6726</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" t="s">
         <v>52</v>
       </c>
-      <c r="B56">
+      <c r="C56">
         <v>7316</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>87</v>
+      </c>
+      <c r="B57" t="s">
         <v>53</v>
       </c>
-      <c r="B57">
+      <c r="C57">
         <v>12980</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" t="s">
         <v>54</v>
       </c>
-      <c r="B58">
+      <c r="C58">
         <v>14750</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>87</v>
+      </c>
+      <c r="B59" t="s">
         <v>55</v>
       </c>
-      <c r="B59">
+      <c r="C59">
         <v>16520</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60" t="s">
         <v>56</v>
       </c>
-      <c r="B60">
+      <c r="C60">
         <v>17700</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" t="s">
         <v>57</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>24780</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" t="s">
         <v>58</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>27140</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" t="s">
         <v>59</v>
       </c>
-      <c r="B63">
+      <c r="C63">
         <v>30090</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>87</v>
+      </c>
+      <c r="B64" t="s">
         <v>60</v>
       </c>
-      <c r="B64">
+      <c r="C64">
         <v>45430</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>87</v>
+      </c>
+      <c r="B65" t="s">
         <v>61</v>
       </c>
-      <c r="B65">
+      <c r="C65">
         <v>51330</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>88</v>
+      </c>
+      <c r="B67" t="s">
         <v>62</v>
       </c>
-      <c r="B67">
+      <c r="C67">
         <v>8850</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B68" t="s">
         <v>63</v>
       </c>
-      <c r="B68">
+      <c r="C68">
         <v>11800</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" t="s">
         <v>64</v>
       </c>
-      <c r="B69">
+      <c r="C69">
         <v>17700</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>88</v>
+      </c>
+      <c r="B70" t="s">
         <v>65</v>
       </c>
-      <c r="B70">
+      <c r="C70">
         <v>18290</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>88</v>
+      </c>
+      <c r="B71" t="s">
         <v>66</v>
       </c>
-      <c r="B71">
+      <c r="C71">
         <v>18880</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72" t="s">
         <v>67</v>
       </c>
-      <c r="B72">
+      <c r="C72">
         <v>19470</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73" t="s">
         <v>68</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>20060</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>88</v>
+      </c>
+      <c r="B74" t="s">
         <v>69</v>
       </c>
-      <c r="B74">
+      <c r="C74">
         <v>20060</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75" t="s">
         <v>70</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>21240</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" t="s">
         <v>71</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>27140</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" t="s">
         <v>72</v>
       </c>
-      <c r="B78">
+      <c r="C78">
         <v>30680</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" t="s">
         <v>73</v>
       </c>
-      <c r="B79">
+      <c r="C79">
         <v>31510</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" t="s">
         <v>74</v>
       </c>
-      <c r="B80">
+      <c r="C80">
         <v>32450</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" t="s">
         <v>75</v>
       </c>
-      <c r="B81">
+      <c r="C81">
         <v>32450</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" t="s">
         <v>76</v>
       </c>
-      <c r="B82">
+      <c r="C82">
         <v>33040</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" t="s">
         <v>77</v>
       </c>
-      <c r="B83">
+      <c r="C83">
         <v>34220</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" t="s">
         <v>78</v>
       </c>
-      <c r="B85">
+      <c r="C85">
         <v>50740</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" t="s">
         <v>79</v>
       </c>
-      <c r="B87">
+      <c r="C87">
         <v>94400</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" t="s">
         <v>80</v>
       </c>
-      <c r="B88">
+      <c r="C88">
         <v>188800</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
         <v>81</v>
       </c>
-      <c r="B89">
+      <c r="C89">
         <v>389400</v>
       </c>
     </row>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -270,9 +270,6 @@
     <t>CPU or Processor</t>
   </si>
   <si>
-    <t>GPU</t>
-  </si>
-  <si>
     <t>Nvidia GPU</t>
   </si>
   <si>
@@ -283,6 +280,9 @@
   </si>
   <si>
     <t>RAM</t>
+  </si>
+  <si>
+    <t>Quadro GPU</t>
   </si>
 </sst>
 </file>
@@ -729,7 +729,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -740,7 +740,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -784,7 +784,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
@@ -828,7 +828,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s">
         <v>27</v>
@@ -927,7 +927,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
         <v>28</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
         <v>29</v>
@@ -949,7 +949,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
         <v>30</v>
@@ -960,7 +960,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
@@ -982,7 +982,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
         <v>33</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
         <v>35</v>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
         <v>36</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
         <v>37</v>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
         <v>38</v>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
         <v>39</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
         <v>40</v>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
         <v>41</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
         <v>42</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
         <v>43</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B46" t="s">
         <v>44</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B47" t="s">
         <v>45</v>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B48" t="s">
         <v>46</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B49" t="s">
         <v>47</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s">
         <v>48</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B52" t="s">
         <v>49</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B53" t="s">
         <v>50</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B55" t="s">
         <v>51</v>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B56" t="s">
         <v>52</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B57" t="s">
         <v>53</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B58" t="s">
         <v>54</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B59" t="s">
         <v>55</v>
@@ -1235,7 +1235,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B60" t="s">
         <v>56</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B61" t="s">
         <v>57</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
         <v>58</v>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
         <v>59</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
         <v>60</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B65" t="s">
         <v>61</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B67" t="s">
         <v>62</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B68" t="s">
         <v>63</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B69" t="s">
         <v>64</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
         <v>65</v>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B71" t="s">
         <v>66</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B72" t="s">
         <v>67</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
         <v>68</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B74" t="s">
         <v>69</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B75" t="s">
         <v>70</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B77" t="s">
         <v>71</v>
@@ -1411,7 +1411,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B78" t="s">
         <v>72</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B79" t="s">
         <v>73</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B80" t="s">
         <v>74</v>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B81" t="s">
         <v>75</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B82" t="s">
         <v>76</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B83" t="s">
         <v>77</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="s">
         <v>78</v>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B87" t="s">
         <v>79</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88" t="s">
         <v>80</v>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
         <v>81</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -270,19 +270,19 @@
     <t>CPU or Processor</t>
   </si>
   <si>
-    <t>Nvidia GPU</t>
-  </si>
-  <si>
-    <t>AMD GPU</t>
-  </si>
-  <si>
     <t>SSD</t>
   </si>
   <si>
     <t>RAM</t>
   </si>
   <si>
-    <t>Quadro GPU</t>
+    <t>GPU or Nvidia</t>
+  </si>
+  <si>
+    <t>GPU or AMD</t>
+  </si>
+  <si>
+    <t>GPU or Quadro</t>
   </si>
 </sst>
 </file>
@@ -729,7 +729,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -740,7 +740,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -784,7 +784,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
@@ -828,7 +828,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
         <v>27</v>
@@ -927,7 +927,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
         <v>28</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
         <v>29</v>
@@ -949,7 +949,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
         <v>30</v>
@@ -960,7 +960,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
@@ -982,7 +982,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
         <v>33</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
         <v>35</v>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
         <v>36</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
         <v>37</v>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
         <v>38</v>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
         <v>39</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
         <v>40</v>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
         <v>41</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
         <v>42</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
         <v>43</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B46" t="s">
         <v>44</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B47" t="s">
         <v>45</v>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
         <v>46</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B49" t="s">
         <v>47</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B50" t="s">
         <v>48</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B55" t="s">
         <v>51</v>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B56" t="s">
         <v>52</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B57" t="s">
         <v>53</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B58" t="s">
         <v>54</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B59" t="s">
         <v>55</v>
@@ -1235,7 +1235,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B60" t="s">
         <v>56</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B61" t="s">
         <v>57</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
         <v>58</v>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
         <v>59</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
         <v>60</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B65" t="s">
         <v>61</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B67" t="s">
         <v>62</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
         <v>63</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B69" t="s">
         <v>64</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B70" t="s">
         <v>65</v>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B71" t="s">
         <v>66</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B72" t="s">
         <v>67</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B73" t="s">
         <v>68</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B74" t="s">
         <v>69</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B75" t="s">
         <v>70</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B77" t="s">
         <v>71</v>
@@ -1411,7 +1411,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B78" t="s">
         <v>72</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B79" t="s">
         <v>73</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B80" t="s">
         <v>74</v>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
         <v>75</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B82" t="s">
         <v>76</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B83" t="s">
         <v>77</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
         <v>78</v>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
         <v>79</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B88" t="s">
         <v>80</v>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B89" t="s">
         <v>81</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -11,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
   <si>
     <t>Component</t>
   </si>
@@ -30,51 +30,27 @@
     <t>9700X</t>
   </si>
   <si>
-    <t>7800X3D</t>
-  </si>
-  <si>
     <t>9900X</t>
   </si>
   <si>
-    <t>9800X3D</t>
-  </si>
-  <si>
-    <t>9900X3D</t>
-  </si>
-  <si>
     <t>9950X</t>
   </si>
   <si>
-    <t>9950X3D</t>
-  </si>
-  <si>
     <t>5060 x2 oc (black)</t>
   </si>
   <si>
     <t>5060 x2 oc (white)</t>
   </si>
   <si>
-    <t>5060 8GB twin edge</t>
-  </si>
-  <si>
     <t>5060 8GB twin edge oc (white)</t>
   </si>
   <si>
-    <t>5060Ti 8GB twin edge oc</t>
-  </si>
-  <si>
     <t>5060Ti 16GB Colorful battle axe duo</t>
   </si>
   <si>
     <t>5060Ti 16GB twin edge</t>
   </si>
   <si>
-    <t>5060Ti 16GB Asus Dual</t>
-  </si>
-  <si>
-    <t>5060Ti 16GB Asus Dual OC</t>
-  </si>
-  <si>
     <t>5060Ti 16GB AMP!</t>
   </si>
   <si>
@@ -156,9 +132,6 @@
     <t>RX 9060XT 16GB (Asus) Dual OC</t>
   </si>
   <si>
-    <t>RX 9070 16GB (Asrock) Challenger OC</t>
-  </si>
-  <si>
     <t>RX 9070XT 16GB (Sapphire) Pulse</t>
   </si>
   <si>
@@ -168,9 +141,6 @@
     <t>RTX Pro 4000 Blackwell 24GB</t>
   </si>
   <si>
-    <t>RTX Pro 6000 Blackwell 96GB</t>
-  </si>
-  <si>
     <t>512GB Gen3</t>
   </si>
   <si>
@@ -180,90 +150,12 @@
     <t>1TB Gen3</t>
   </si>
   <si>
-    <t>1TB Gen4 6000mbps</t>
-  </si>
-  <si>
-    <t>1TB Gen4 7000mbps</t>
-  </si>
-  <si>
     <t>1TB Gen5 P510 Crucial</t>
   </si>
   <si>
-    <t>2TB Gen4 6000</t>
-  </si>
-  <si>
-    <t>2TB Gen4 7000</t>
-  </si>
-  <si>
     <t>2TB Gen5 P510 Crucial</t>
   </si>
   <si>
-    <t>4TB Gen4 7000</t>
-  </si>
-  <si>
-    <t>4TB Gen5 XPG</t>
-  </si>
-  <si>
-    <t>16GB DDR4 3200 (EVM)</t>
-  </si>
-  <si>
-    <t>16GB DDR4 3600 (T.Force Vulcan)</t>
-  </si>
-  <si>
-    <t>16GB DDR5 5200 (Ripjaws V)</t>
-  </si>
-  <si>
-    <t>16GB DDR5 5600 (Ripjaws V)</t>
-  </si>
-  <si>
-    <t>16GB DDR5 6000 (Ripjaws V)</t>
-  </si>
-  <si>
-    <t>16GB DDR5 6000 CL32</t>
-  </si>
-  <si>
-    <t>16GB DDR5 6000 RGB CL36</t>
-  </si>
-  <si>
-    <t>16GB DDR5 6000 CL30</t>
-  </si>
-  <si>
-    <t>16GB DDR5 6000 RGB CL30</t>
-  </si>
-  <si>
-    <t>32GB DDR5 5200 (Nextron)</t>
-  </si>
-  <si>
-    <t>32GB DDR5 5200</t>
-  </si>
-  <si>
-    <t>32GB DDR5 5600</t>
-  </si>
-  <si>
-    <t>32GB DDR5 6000</t>
-  </si>
-  <si>
-    <t>32GB DDR5 5600 RGB CL36</t>
-  </si>
-  <si>
-    <t>32GB DDR5 6000 RGB CL36</t>
-  </si>
-  <si>
-    <t>32GB DDR5 6000 RGB CL30</t>
-  </si>
-  <si>
-    <t>48GB DDR5 6000 RGB CL28</t>
-  </si>
-  <si>
-    <t>32GB DDR5 ECC RDIMM</t>
-  </si>
-  <si>
-    <t>64GB DDR5 ECC RDIMM</t>
-  </si>
-  <si>
-    <t>128GB DDR5 ECC RDIMM</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
@@ -283,6 +175,111 @@
   </si>
   <si>
     <t>GPU or Quadro</t>
+  </si>
+  <si>
+    <t>7800X 3D</t>
+  </si>
+  <si>
+    <t>9800X 3D</t>
+  </si>
+  <si>
+    <t>9900X 3D</t>
+  </si>
+  <si>
+    <t>9950X 3D</t>
+  </si>
+  <si>
+    <t>5060 8GB twin edge oc</t>
+  </si>
+  <si>
+    <t>RTX 5060Ti 8GB twin edge oc</t>
+  </si>
+  <si>
+    <t>5060TI 16GB Asus Dual OC</t>
+  </si>
+  <si>
+    <t>RX 9070 16GB (Asrock) Challenger OC 3-Fan</t>
+  </si>
+  <si>
+    <t>RTX Pro 6000 Blackwell 96GB Workstation Edition</t>
+  </si>
+  <si>
+    <t>1TB Gen4 6000mbps or slower</t>
+  </si>
+  <si>
+    <t>1TB Gen4 7000mbps or faster</t>
+  </si>
+  <si>
+    <t>2TB Gen4 6000 or slower</t>
+  </si>
+  <si>
+    <t>2TB Gen4 7000 or faster</t>
+  </si>
+  <si>
+    <t>4TB Gen4 7000 or faster</t>
+  </si>
+  <si>
+    <t>4TB Gen5 xpg</t>
+  </si>
+  <si>
+    <t>16GB DDR4 3200 (16*1) (EVM)</t>
+  </si>
+  <si>
+    <t>16GB DDR4 3600 (16*1) (T.Force Vulcan)</t>
+  </si>
+  <si>
+    <t>16GB DDR5 5200 (16*1) (Ripjaws V)</t>
+  </si>
+  <si>
+    <t>16GB DDR5 5600 (16*1) (Ripjaws V)</t>
+  </si>
+  <si>
+    <t>16GB DDR5 6000 (16*1) (Ripjaws V)</t>
+  </si>
+  <si>
+    <t>16GB DDR5 6000 (16*1) CL32</t>
+  </si>
+  <si>
+    <t>16GB DDR5 6000 (16*1) RGB CL36</t>
+  </si>
+  <si>
+    <t>16GB DDR5 6000 (16*1) CL30</t>
+  </si>
+  <si>
+    <t>16GB DDR5 6000 (16*1) RGB CL30</t>
+  </si>
+  <si>
+    <t>32GB DDR5 5200 (32*1) (Nextron)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 5200 (32*1)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 5600 (32*1)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 6000 (32*1)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 5600 RGB CL36 (32*1)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 6000 RGB CL36 (32*1)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 6000 RGB CL30 (32*1)</t>
+  </si>
+  <si>
+    <t>48GB DDR5 6000 RGB CL28 (48*1)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 ECC RDIMM 5600MT/s (32*1)</t>
+  </si>
+  <si>
+    <t>64GB DDR5 ECC RDIMM 5600MT/s (64*1)</t>
+  </si>
+  <si>
+    <t>128GB DDR5 ECC RDIMM 5600MT/s (128*1)</t>
   </si>
 </sst>
 </file>
@@ -621,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -630,7 +627,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -641,7 +638,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -652,32 +649,32 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3">
-        <v>28910</v>
+        <v>27140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C4">
-        <v>37760</v>
+        <v>35990</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>43070</v>
@@ -685,21 +682,21 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="C6">
-        <v>46610</v>
+        <v>44840</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>57820</v>
@@ -707,21 +704,21 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>53100</v>
+        <v>50150</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>70210</v>
@@ -729,10 +726,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>36580</v>
@@ -740,10 +737,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>36580</v>
@@ -751,10 +748,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="C13">
         <v>37760</v>
@@ -762,21 +759,21 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>38940</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>44840</v>
@@ -784,219 +781,219 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>60180</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>61360</v>
+        <v>60770</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="C18">
-        <v>61360</v>
+        <v>61950</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>62540</v>
+        <v>63130</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C20">
-        <v>63720</v>
+        <v>72570</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C21">
-        <v>73750</v>
+        <v>71390</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C22">
-        <v>72570</v>
+        <v>69030</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C23">
-        <v>70800</v>
+        <v>104430</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>108560</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C25">
-        <v>108560</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C26">
-        <v>110920</v>
+        <v>108560</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>110920</v>
+        <v>139240</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C28">
-        <v>141600</v>
+        <v>145140</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C29">
-        <v>149860</v>
+        <v>146320</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C30">
-        <v>149860</v>
+        <v>146320</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C31">
-        <v>149860</v>
+        <v>146320</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C32">
-        <v>149860</v>
+        <v>158120</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C33">
-        <v>162840</v>
+        <v>354000</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C34">
-        <v>354000</v>
+        <v>389400</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C35">
         <v>389400</v>
@@ -1004,21 +1001,21 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C36">
-        <v>389400</v>
+        <v>395300</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C37">
         <v>395300</v>
@@ -1026,87 +1023,87 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C38">
-        <v>395300</v>
+        <v>407100</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C39">
-        <v>407100</v>
+        <v>418900</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C40">
-        <v>424800</v>
+        <v>430700</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C41">
-        <v>436600</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42">
         <v>495600</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43">
+        <v>24190</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C44">
-        <v>24780</v>
+        <v>31270</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C45">
-        <v>31270</v>
+        <v>47200</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C46">
         <v>47200</v>
@@ -1114,413 +1111,403 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C47">
-        <v>48380</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C48">
-        <v>59590</v>
+        <v>72570</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C49">
-        <v>73750</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>87</v>
-      </c>
-      <c r="B50" t="s">
-        <v>48</v>
-      </c>
-      <c r="C50">
-        <v>75520</v>
+        <v>74340</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51">
+        <v>161660</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C52">
-        <v>159300</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>88</v>
-      </c>
-      <c r="B53" t="s">
-        <v>50</v>
-      </c>
-      <c r="C53">
         <v>920400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54">
+        <v>6844</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C55">
-        <v>6726</v>
+        <v>7316</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C56">
-        <v>7316</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C57">
-        <v>12980</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C58">
-        <v>14750</v>
+        <v>16520</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C59">
-        <v>16520</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C60">
-        <v>17700</v>
+        <v>24190</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C61">
-        <v>24780</v>
+        <v>27140</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C62">
-        <v>27140</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C63">
-        <v>30090</v>
+        <v>43660</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B64" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C64">
-        <v>45430</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>84</v>
-      </c>
-      <c r="B65" t="s">
-        <v>61</v>
-      </c>
-      <c r="C65">
-        <v>51330</v>
+        <v>49560</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>49</v>
+      </c>
+      <c r="B66" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66">
+        <v>8850</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C67">
-        <v>8850</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C68">
-        <v>11800</v>
+        <v>17936</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B69" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C69">
-        <v>17700</v>
+        <v>18880</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C70">
-        <v>18290</v>
+        <v>19706</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C71">
-        <v>18880</v>
+        <v>20296</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C72">
-        <v>19470</v>
+        <v>20886</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C73">
-        <v>20060</v>
+        <v>21004</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B74" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C74">
-        <v>20060</v>
+        <v>22184</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C75">
-        <v>21240</v>
+        <v>27730</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>49</v>
+      </c>
+      <c r="B76" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76">
+        <v>31270</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C77">
-        <v>27140</v>
+        <v>32450</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C78">
-        <v>30680</v>
+        <v>33630</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B79" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C79">
-        <v>31510</v>
+        <v>33630</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B80" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C80">
-        <v>32450</v>
+        <v>34810</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C81">
-        <v>32450</v>
+        <v>36580</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B82" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C82">
-        <v>33040</v>
+        <v>50740</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>49</v>
+      </c>
+      <c r="B83" t="s">
         <v>85</v>
       </c>
-      <c r="B83" t="s">
-        <v>77</v>
-      </c>
       <c r="C83">
-        <v>34220</v>
+        <v>100300</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>49</v>
+      </c>
+      <c r="B84" t="s">
+        <v>86</v>
+      </c>
+      <c r="C84">
+        <v>212400</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B85" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C85">
-        <v>50740</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>85</v>
-      </c>
-      <c r="B87" t="s">
-        <v>79</v>
-      </c>
-      <c r="C87">
-        <v>94400</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>85</v>
-      </c>
-      <c r="B88" t="s">
-        <v>80</v>
-      </c>
-      <c r="C88">
-        <v>188800</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>85</v>
-      </c>
-      <c r="B89" t="s">
-        <v>81</v>
-      </c>
-      <c r="C89">
-        <v>389400</v>
+        <v>401200</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -228,15 +228,6 @@
     <t>16GB DDR4 3600 (16*1) (T.Force Vulcan)</t>
   </si>
   <si>
-    <t>16GB DDR5 5200 (16*1) (Ripjaws V)</t>
-  </si>
-  <si>
-    <t>16GB DDR5 5600 (16*1) (Ripjaws V)</t>
-  </si>
-  <si>
-    <t>16GB DDR5 6000 (16*1) (Ripjaws V)</t>
-  </si>
-  <si>
     <t>16GB DDR5 6000 (16*1) CL32</t>
   </si>
   <si>
@@ -252,15 +243,9 @@
     <t>32GB DDR5 5200 (32*1) (Nextron)</t>
   </si>
   <si>
-    <t>32GB DDR5 5200 (32*1)</t>
-  </si>
-  <si>
     <t>32GB DDR5 5600 (32*1)</t>
   </si>
   <si>
-    <t>32GB DDR5 6000 (32*1)</t>
-  </si>
-  <si>
     <t>32GB DDR5 5600 RGB CL36 (32*1)</t>
   </si>
   <si>
@@ -270,9 +255,6 @@
     <t>32GB DDR5 6000 RGB CL30 (32*1)</t>
   </si>
   <si>
-    <t>48GB DDR5 6000 RGB CL28 (48*1)</t>
-  </si>
-  <si>
     <t>32GB DDR5 ECC RDIMM 5600MT/s (32*1)</t>
   </si>
   <si>
@@ -280,6 +262,24 @@
   </si>
   <si>
     <t>128GB DDR5 ECC RDIMM 5600MT/s (128*1)</t>
+  </si>
+  <si>
+    <t>16GB DDR5 5200 (16*1) (Ripjaws S5 CL40)</t>
+  </si>
+  <si>
+    <t>16GB DDR5 5600 (16*1) (Ripjaws S5 CL40)</t>
+  </si>
+  <si>
+    <t>16GB DDR5 6000 (16*1) (Ripjaws S5 CL36)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 5200 (32*1) (Ripjaws s5 CL40) (DO NOT GIVE)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 6000 (32*1) (Ripjaws s5 CL36)</t>
+  </si>
+  <si>
+    <t>48GB DDR5 6000 RGB CL28 (48*1) (BiWin DW100)</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1312,7 @@
         <v>49</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C68">
         <v>17936</v>
@@ -1323,7 +1323,7 @@
         <v>49</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C69">
         <v>18880</v>
@@ -1334,7 +1334,7 @@
         <v>49</v>
       </c>
       <c r="B70" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C70">
         <v>19706</v>
@@ -1345,7 +1345,7 @@
         <v>49</v>
       </c>
       <c r="B71" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C71">
         <v>20296</v>
@@ -1356,10 +1356,10 @@
         <v>49</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C72">
-        <v>20886</v>
+        <v>21004</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>49</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C73">
-        <v>21004</v>
+        <v>20886</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
         <v>49</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C74">
         <v>22184</v>
@@ -1389,7 +1389,7 @@
         <v>49</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C75">
         <v>27730</v>
@@ -1400,7 +1400,7 @@
         <v>49</v>
       </c>
       <c r="B76" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C76">
         <v>31270</v>
@@ -1411,7 +1411,7 @@
         <v>49</v>
       </c>
       <c r="B77" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C77">
         <v>32450</v>
@@ -1422,7 +1422,7 @@
         <v>49</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C78">
         <v>33630</v>
@@ -1433,7 +1433,7 @@
         <v>49</v>
       </c>
       <c r="B79" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C79">
         <v>33630</v>
@@ -1444,7 +1444,7 @@
         <v>49</v>
       </c>
       <c r="B80" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C80">
         <v>34810</v>
@@ -1455,7 +1455,7 @@
         <v>49</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C81">
         <v>36580</v>
@@ -1466,7 +1466,7 @@
         <v>49</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C82">
         <v>50740</v>
@@ -1477,7 +1477,7 @@
         <v>49</v>
       </c>
       <c r="B83" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C83">
         <v>100300</v>
@@ -1488,7 +1488,7 @@
         <v>49</v>
       </c>
       <c r="B84" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C84">
         <v>212400</v>
@@ -1499,7 +1499,7 @@
         <v>49</v>
       </c>
       <c r="B85" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C85">
         <v>401200</v>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="86">
   <si>
     <t>Component</t>
   </si>
@@ -57,9 +57,6 @@
     <t>5070 inspire 3x oc</t>
   </si>
   <si>
-    <t>5070 Zotac Solid</t>
-  </si>
-  <si>
     <t>5070 Zotac Twin Edge</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>5080 igame Ultra (White)</t>
   </si>
   <si>
-    <t>5080 Ventus 3X oc plus</t>
-  </si>
-  <si>
     <t>5080 Inspire 3X OC</t>
   </si>
   <si>
@@ -114,9 +108,6 @@
     <t>5090 Arctic Storm AIO</t>
   </si>
   <si>
-    <t>5090 MSI Suprim Liquid</t>
-  </si>
-  <si>
     <t>5090 ASUS Matrix</t>
   </si>
   <si>
@@ -141,9 +132,6 @@
     <t>RTX Pro 4000 Blackwell 24GB</t>
   </si>
   <si>
-    <t>512GB Gen3</t>
-  </si>
-  <si>
     <t>512GB Gen4</t>
   </si>
   <si>
@@ -264,22 +252,28 @@
     <t>128GB DDR5 ECC RDIMM 5600MT/s (128*1)</t>
   </si>
   <si>
-    <t>16GB DDR5 5200 (16*1) (Ripjaws S5 CL40)</t>
-  </si>
-  <si>
-    <t>16GB DDR5 5600 (16*1) (Ripjaws S5 CL40)</t>
-  </si>
-  <si>
-    <t>16GB DDR5 6000 (16*1) (Ripjaws S5 CL36)</t>
-  </si>
-  <si>
-    <t>32GB DDR5 5200 (32*1) (Ripjaws s5 CL40) (DO NOT GIVE)</t>
-  </si>
-  <si>
-    <t>32GB DDR5 6000 (32*1) (Ripjaws s5 CL36)</t>
-  </si>
-  <si>
-    <t>48GB DDR5 6000 RGB CL28 (48*1) (BiWin DW100)</t>
+    <t>5070 Zotac Solid OC</t>
+  </si>
+  <si>
+    <t>5080 Ventus 3X oc</t>
+  </si>
+  <si>
+    <t>16GB DDR5 5200 (16*1) (Ripjaws V)</t>
+  </si>
+  <si>
+    <t>16GB DDR5 5600 (16*1) (Ripjaws V)</t>
+  </si>
+  <si>
+    <t>16GB DDR5 6000 (16*1) (Ripjaws V)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 5200 (32*1)</t>
+  </si>
+  <si>
+    <t>32GB DDR5 6000 (32*1)</t>
+  </si>
+  <si>
+    <t>48GB DDR5 6000 RGB CL28 (48*1)</t>
   </si>
 </sst>
 </file>
@@ -618,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -627,7 +621,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -638,18 +632,18 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>14042</v>
+        <v>13570</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -660,10 +654,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>35990</v>
@@ -671,318 +665,329 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5">
-        <v>43070</v>
+        <v>42480</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C6">
-        <v>44840</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C7">
-        <v>57820</v>
+        <v>56640</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8">
-        <v>50150</v>
+        <v>49560</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C9">
-        <v>70210</v>
+        <v>69620</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>33040</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>36580</v>
+        <v>33040</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C12">
-        <v>36580</v>
+        <v>34220</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>37760</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C14">
-        <v>38350</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>44840</v>
+        <v>56640</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>59000</v>
+        <v>57820</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C17">
-        <v>60770</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C18">
-        <v>61950</v>
+        <v>60180</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19">
-        <v>63130</v>
+        <v>70210</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="C20">
-        <v>72570</v>
+        <v>69620</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
       <c r="C21">
-        <v>71390</v>
+        <v>67260</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
       </c>
       <c r="C22">
-        <v>69030</v>
+        <v>102660</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23">
-        <v>104430</v>
+        <v>103840</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24">
-        <v>106200</v>
+        <v>103840</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
       </c>
       <c r="C25">
-        <v>106200</v>
+        <v>105610</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
         <v>18</v>
       </c>
       <c r="C26">
-        <v>108560</v>
+        <v>134520</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27">
-        <v>139240</v>
+        <v>138060</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C28">
-        <v>145140</v>
+        <v>136880</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="C29">
-        <v>146320</v>
+        <v>138060</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C30">
-        <v>146320</v>
+        <v>141010</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31">
-        <v>146320</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32">
-        <v>158120</v>
+        <v>354000</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33">
-        <v>354000</v>
+        <v>389400</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C34">
         <v>389400</v>
@@ -990,21 +995,21 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C35">
-        <v>389400</v>
+        <v>395300</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C36">
         <v>395300</v>
@@ -1012,496 +1017,463 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C37">
-        <v>395300</v>
+        <v>407100</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38">
-        <v>407100</v>
+        <v>418900</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39">
-        <v>418900</v>
+        <v>495600</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C40">
-        <v>430700</v>
+        <v>25370</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41">
+        <v>29500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" t="s">
         <v>33</v>
       </c>
-      <c r="C41">
-        <v>495600</v>
+      <c r="C42">
+        <v>43660</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
         <v>34</v>
       </c>
       <c r="C43">
-        <v>24190</v>
+        <v>44840</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C44">
-        <v>31270</v>
+        <v>55460</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C45">
-        <v>47200</v>
+        <v>69620</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C46">
-        <v>47200</v>
+        <v>71980</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C47">
-        <v>59000</v>
+        <v>172280</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C48">
-        <v>72570</v>
+        <v>920400</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49">
+        <v>6962</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" t="s">
         <v>39</v>
       </c>
-      <c r="C49">
-        <v>74340</v>
+      <c r="C50">
+        <v>11210</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C51">
-        <v>161660</v>
+        <v>14160</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C52">
-        <v>920400</v>
+        <v>15930</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53">
+        <v>17700</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C54">
-        <v>6844</v>
+        <v>24190</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C55">
-        <v>7316</v>
+        <v>27140</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C56">
-        <v>11800</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B57" t="s">
         <v>62</v>
       </c>
       <c r="C57">
-        <v>14750</v>
+        <v>44840</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B58" t="s">
         <v>63</v>
       </c>
       <c r="C58">
-        <v>16520</v>
+        <v>50740</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C59">
-        <v>17700</v>
+        <v>8024</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C60">
-        <v>24190</v>
+        <v>10974</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C61">
-        <v>27140</v>
+        <v>15340</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C62">
-        <v>29500</v>
+        <v>16520</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C63">
-        <v>43660</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64">
+        <v>18290</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" t="s">
         <v>67</v>
       </c>
-      <c r="C64">
-        <v>49560</v>
+      <c r="C65">
+        <v>18880</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
         <v>68</v>
       </c>
       <c r="C66">
-        <v>8850</v>
+        <v>18880</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
         <v>69</v>
       </c>
       <c r="C67">
-        <v>11800</v>
+        <v>19824</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C68">
-        <v>17936</v>
+        <v>26550</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
         <v>83</v>
       </c>
       <c r="C69">
-        <v>18880</v>
+        <v>28910</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C70">
-        <v>19706</v>
+        <v>29736</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C71">
-        <v>20296</v>
+        <v>30680</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
         <v>72</v>
       </c>
       <c r="C72">
-        <v>21004</v>
+        <v>30680</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C73">
-        <v>20886</v>
+        <v>31860</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C74">
-        <v>22184</v>
+        <v>33040</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C75">
-        <v>27730</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C76">
-        <v>31270</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C77">
-        <v>32450</v>
+        <v>200600</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C78">
-        <v>33630</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>49</v>
-      </c>
-      <c r="B79" t="s">
-        <v>76</v>
-      </c>
-      <c r="C79">
-        <v>33630</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>49</v>
-      </c>
-      <c r="B80" t="s">
-        <v>77</v>
-      </c>
-      <c r="C80">
-        <v>34810</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>49</v>
-      </c>
-      <c r="B81" t="s">
-        <v>78</v>
-      </c>
-      <c r="C81">
-        <v>36580</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>49</v>
-      </c>
-      <c r="B82" t="s">
-        <v>87</v>
-      </c>
-      <c r="C82">
-        <v>50740</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>49</v>
-      </c>
-      <c r="B83" t="s">
-        <v>79</v>
-      </c>
-      <c r="C83">
-        <v>100300</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>49</v>
-      </c>
-      <c r="B84" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84">
-        <v>212400</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>49</v>
-      </c>
-      <c r="B85" t="s">
-        <v>81</v>
-      </c>
-      <c r="C85">
         <v>401200</v>
       </c>
     </row>
